--- a/Data/tabular/YBLTE_fish_specimens.xlsx
+++ b/Data/tabular/YBLTE_fish_specimens.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kristinn\Downloads\coding\YBLTE\Data\tabular\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA110F7-585C-4C14-A06A-5F801175963B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5ECDA1-1713-4A06-9315-4EC4B29BB0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="10800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Juv_CHN_take_2026" sheetId="1" r:id="rId1"/>
     <sheet name="not_databased" sheetId="2" r:id="rId2"/>
-    <sheet name="Total Fish" sheetId="3" r:id="rId3"/>
-    <sheet name="Counts by Habitat" sheetId="4" r:id="rId4"/>
-    <sheet name="Counts by Date" sheetId="5" r:id="rId5"/>
+    <sheet name="Bridge Group" sheetId="6" r:id="rId3"/>
+    <sheet name="Total Fish" sheetId="3" r:id="rId4"/>
+    <sheet name="Counts by Habitat" sheetId="4" r:id="rId5"/>
+    <sheet name="Counts by Date" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="121">
   <si>
     <t>CNW</t>
   </si>
@@ -375,6 +376,18 @@
   </si>
   <si>
     <t>count</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>Done manually w/ search on excel (not many)</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Station</t>
   </si>
 </sst>
 </file>
@@ -535,7 +548,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -833,12 +846,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S59"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="17.81640625" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -897,30 +911,30 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>11437</v>
+        <v>11453</v>
       </c>
       <c r="B2" s="12">
-        <v>46036</v>
+        <v>46044</v>
       </c>
       <c r="C2" s="12">
-        <v>1.41875000000073</v>
+        <v>1.4555555555562001</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H2">
-        <v>0.37999999523162797</v>
+        <v>0.20999999344348899</v>
       </c>
       <c r="I2" t="s">
         <v>42</v>
@@ -932,19 +946,19 @@
         <v>44</v>
       </c>
       <c r="L2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
       </c>
       <c r="N2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -956,18 +970,18 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>11434</v>
+        <v>11459</v>
       </c>
       <c r="B3" s="12">
-        <v>46036</v>
+        <v>46044</v>
       </c>
       <c r="C3" s="12">
-        <v>1.48611111110949</v>
+        <v>1.46666666666715</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
         <v>40</v>
@@ -976,10 +990,10 @@
         <v>41</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H3">
-        <v>0.57999998331069902</v>
+        <v>0.55849999189376798</v>
       </c>
       <c r="I3" t="s">
         <v>42</v>
@@ -991,19 +1005,19 @@
         <v>44</v>
       </c>
       <c r="L3" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -1015,18 +1029,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>11455</v>
+        <v>11459</v>
       </c>
       <c r="B4" s="12">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="C4" s="12">
-        <v>1.40972222222263</v>
+        <v>1.46666666666715</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
         <v>40</v>
@@ -1035,10 +1049,10 @@
         <v>41</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H4">
-        <v>0.62999999523162797</v>
+        <v>0.44800001382827798</v>
       </c>
       <c r="I4" t="s">
         <v>42</v>
@@ -1050,19 +1064,19 @@
         <v>44</v>
       </c>
       <c r="L4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
       </c>
       <c r="N4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -1074,30 +1088,30 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>11453</v>
+        <v>11459</v>
       </c>
       <c r="B5" s="12">
         <v>46044</v>
       </c>
       <c r="C5" s="12">
-        <v>1.4555555555562001</v>
+        <v>1.46666666666715</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
         <v>41</v>
       </c>
       <c r="G5">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H5">
-        <v>0.20999999344348899</v>
+        <v>0.63400000333786</v>
       </c>
       <c r="I5" t="s">
         <v>42</v>
@@ -1121,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -1130,21 +1144,21 @@
         <v>0</v>
       </c>
       <c r="S5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>11459</v>
+        <v>11511</v>
       </c>
       <c r="B6" s="12">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="C6" s="12">
-        <v>1.46666666666715</v>
+        <v>1.4229166666664199</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
         <v>40</v>
@@ -1156,7 +1170,7 @@
         <v>41</v>
       </c>
       <c r="H6">
-        <v>0.55849999189376798</v>
+        <v>0.56999999284744296</v>
       </c>
       <c r="I6" t="s">
         <v>42</v>
@@ -1179,9 +1193,6 @@
       <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="s">
-        <v>58</v>
-      </c>
       <c r="Q6">
         <v>1</v>
       </c>
@@ -1189,21 +1200,21 @@
         <v>0</v>
       </c>
       <c r="S6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>11459</v>
+        <v>11511</v>
       </c>
       <c r="B7" s="12">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="C7" s="12">
-        <v>1.46666666666715</v>
+        <v>1.4229166666664199</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
         <v>40</v>
@@ -1212,10 +1223,10 @@
         <v>41</v>
       </c>
       <c r="G7">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H7">
-        <v>0.44800001382827798</v>
+        <v>0.70999997854232799</v>
       </c>
       <c r="I7" t="s">
         <v>42</v>
@@ -1238,9 +1249,6 @@
       <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="s">
-        <v>59</v>
-      </c>
       <c r="Q7">
         <v>1</v>
       </c>
@@ -1248,21 +1256,21 @@
         <v>0</v>
       </c>
       <c r="S7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>11459</v>
+        <v>11511</v>
       </c>
       <c r="B8" s="12">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="C8" s="12">
-        <v>1.46666666666715</v>
+        <v>1.4229166666664199</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
         <v>40</v>
@@ -1271,10 +1279,10 @@
         <v>41</v>
       </c>
       <c r="G8">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H8">
-        <v>0.63400000333786</v>
+        <v>0.70999997854232799</v>
       </c>
       <c r="I8" t="s">
         <v>42</v>
@@ -1297,9 +1305,6 @@
       <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="s">
-        <v>60</v>
-      </c>
       <c r="Q8">
         <v>1</v>
       </c>
@@ -1307,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>11511</v>
       </c>
@@ -1330,10 +1335,10 @@
         <v>41</v>
       </c>
       <c r="G9">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H9">
-        <v>0.56999999284744296</v>
+        <v>0.85000002384185802</v>
       </c>
       <c r="I9" t="s">
         <v>42</v>
@@ -1366,7 +1371,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>11511</v>
       </c>
@@ -1386,10 +1391,10 @@
         <v>41</v>
       </c>
       <c r="G10">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H10">
-        <v>0.70999997854232799</v>
+        <v>0.87000000476837203</v>
       </c>
       <c r="I10" t="s">
         <v>42</v>
@@ -1422,18 +1427,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>11511</v>
+        <v>3</v>
       </c>
       <c r="B11" s="12">
-        <v>46045</v>
+        <v>46063</v>
       </c>
       <c r="C11" s="12">
-        <v>1.4229166666664199</v>
+        <v>1.59375</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
         <v>40</v>
@@ -1442,10 +1447,10 @@
         <v>41</v>
       </c>
       <c r="G11">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="H11">
-        <v>0.70999997854232799</v>
+        <v>1.3</v>
       </c>
       <c r="I11" t="s">
         <v>42</v>
@@ -1468,6 +1473,9 @@
       <c r="O11" t="b">
         <v>0</v>
       </c>
+      <c r="P11" t="s">
+        <v>76</v>
+      </c>
       <c r="Q11">
         <v>1</v>
       </c>
@@ -1475,21 +1483,21 @@
         <v>0</v>
       </c>
       <c r="S11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>11511</v>
+        <v>3</v>
       </c>
       <c r="B12" s="12">
-        <v>46045</v>
+        <v>46063</v>
       </c>
       <c r="C12" s="12">
-        <v>1.4229166666664199</v>
+        <v>1.59375</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
         <v>40</v>
@@ -1498,10 +1506,10 @@
         <v>41</v>
       </c>
       <c r="G12">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H12">
-        <v>0.85000002384185802</v>
+        <v>1.28</v>
       </c>
       <c r="I12" t="s">
         <v>42</v>
@@ -1524,6 +1532,9 @@
       <c r="O12" t="b">
         <v>0</v>
       </c>
+      <c r="P12" t="s">
+        <v>77</v>
+      </c>
       <c r="Q12">
         <v>1</v>
       </c>
@@ -1531,21 +1542,21 @@
         <v>0</v>
       </c>
       <c r="S12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>11511</v>
+        <v>3</v>
       </c>
       <c r="B13" s="12">
-        <v>46045</v>
+        <v>46063</v>
       </c>
       <c r="C13" s="12">
-        <v>1.4229166666664199</v>
+        <v>1.59375</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
         <v>40</v>
@@ -1554,444 +1565,447 @@
         <v>41</v>
       </c>
       <c r="G13">
+        <v>48</v>
+      </c>
+      <c r="H13">
+        <v>1.08</v>
+      </c>
+      <c r="I13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" t="s">
+        <v>43</v>
+      </c>
+      <c r="K13" t="s">
+        <v>44</v>
+      </c>
+      <c r="L13" t="s">
+        <v>55</v>
+      </c>
+      <c r="M13" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13" t="b">
+        <v>0</v>
+      </c>
+      <c r="S13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14" s="12">
+        <v>46064</v>
+      </c>
+      <c r="C14" s="12">
+        <v>1.4034722222204401</v>
+      </c>
+      <c r="D14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14">
+        <v>57</v>
+      </c>
+      <c r="H14">
+        <v>1.78</v>
+      </c>
+      <c r="I14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L14" t="s">
+        <v>55</v>
+      </c>
+      <c r="M14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15" s="12">
+        <v>46064</v>
+      </c>
+      <c r="C15" s="12">
+        <v>1.4034722222204401</v>
+      </c>
+      <c r="D15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15">
+        <v>58</v>
+      </c>
+      <c r="H15">
+        <v>2.11</v>
+      </c>
+      <c r="I15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J15" t="s">
+        <v>43</v>
+      </c>
+      <c r="K15" t="s">
+        <v>44</v>
+      </c>
+      <c r="L15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>4</v>
+      </c>
+      <c r="B16" s="12">
+        <v>46064</v>
+      </c>
+      <c r="C16" s="12">
+        <v>1.4034722222204401</v>
+      </c>
+      <c r="D16" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16">
+        <v>56</v>
+      </c>
+      <c r="H16">
+        <v>1.97</v>
+      </c>
+      <c r="I16" t="s">
+        <v>42</v>
+      </c>
+      <c r="J16" t="s">
+        <v>43</v>
+      </c>
+      <c r="K16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M16" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16" t="b">
+        <v>0</v>
+      </c>
+      <c r="S16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>11517</v>
+      </c>
+      <c r="B17" s="12">
+        <v>46064</v>
+      </c>
+      <c r="C17" s="12">
+        <v>1.34375</v>
+      </c>
+      <c r="D17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17">
+        <v>49</v>
+      </c>
+      <c r="H17">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="I17" t="s">
+        <v>42</v>
+      </c>
+      <c r="J17" t="s">
+        <v>43</v>
+      </c>
+      <c r="K17" t="s">
+        <v>44</v>
+      </c>
+      <c r="L17" t="s">
+        <v>55</v>
+      </c>
+      <c r="M17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>11517</v>
+      </c>
+      <c r="B18" s="12">
+        <v>46064</v>
+      </c>
+      <c r="C18" s="12">
+        <v>1.34375</v>
+      </c>
+      <c r="D18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18">
         <v>46</v>
       </c>
-      <c r="H13">
-        <v>0.87000000476837203</v>
-      </c>
-      <c r="I13" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13" t="s">
-        <v>43</v>
-      </c>
-      <c r="K13" t="s">
-        <v>44</v>
-      </c>
-      <c r="L13" t="s">
-        <v>55</v>
-      </c>
-      <c r="M13" t="b">
-        <v>1</v>
-      </c>
-      <c r="N13" t="b">
-        <v>1</v>
-      </c>
-      <c r="O13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>1</v>
-      </c>
-      <c r="R13" t="b">
-        <v>0</v>
-      </c>
-      <c r="S13" t="s">
+      <c r="H18">
+        <v>0.91000002622604403</v>
+      </c>
+      <c r="I18" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" t="s">
+        <v>43</v>
+      </c>
+      <c r="K18" t="s">
+        <v>44</v>
+      </c>
+      <c r="L18" t="s">
+        <v>55</v>
+      </c>
+      <c r="M18" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
+      </c>
+      <c r="O18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>11485</v>
-      </c>
-      <c r="B14" s="12">
-        <v>46057</v>
-      </c>
-      <c r="C14" s="12">
-        <v>1.4312500000014601</v>
-      </c>
-      <c r="D14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14">
-        <v>55</v>
-      </c>
-      <c r="H14">
-        <v>1.8380000591278101</v>
-      </c>
-      <c r="I14" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" t="s">
-        <v>63</v>
-      </c>
-      <c r="K14" t="s">
-        <v>44</v>
-      </c>
-      <c r="L14" t="s">
-        <v>45</v>
-      </c>
-      <c r="M14" t="b">
-        <v>1</v>
-      </c>
-      <c r="N14" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" t="b">
-        <v>1</v>
-      </c>
-      <c r="P14" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q14">
-        <v>1</v>
-      </c>
-      <c r="R14" t="b">
-        <v>0</v>
-      </c>
-      <c r="S14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>11485</v>
-      </c>
-      <c r="B15" s="12">
-        <v>46057</v>
-      </c>
-      <c r="C15" s="12">
-        <v>1.4312500000014601</v>
-      </c>
-      <c r="D15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>11517</v>
+      </c>
+      <c r="B19" s="12">
+        <v>46064</v>
+      </c>
+      <c r="C19" s="12">
+        <v>1.34375</v>
+      </c>
+      <c r="D19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19">
+        <v>50</v>
+      </c>
+      <c r="H19">
+        <v>1.25</v>
+      </c>
+      <c r="I19" t="s">
+        <v>42</v>
+      </c>
+      <c r="J19" t="s">
+        <v>43</v>
+      </c>
+      <c r="K19" t="s">
+        <v>44</v>
+      </c>
+      <c r="L19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
+      </c>
+      <c r="O19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19" t="b">
+        <v>0</v>
+      </c>
+      <c r="S19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>11496</v>
+      </c>
+      <c r="B20" s="12">
+        <v>46066</v>
+      </c>
+      <c r="C20" s="12">
+        <v>1.55069444444598</v>
+      </c>
+      <c r="D20" t="s">
         <v>86</v>
       </c>
-      <c r="H15">
-        <v>5.8803000450134304</v>
-      </c>
-      <c r="I15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J15" t="s">
-        <v>65</v>
-      </c>
-      <c r="K15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L15" t="s">
-        <v>45</v>
-      </c>
-      <c r="M15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N15" t="b">
-        <v>0</v>
-      </c>
-      <c r="O15" t="b">
-        <v>1</v>
-      </c>
-      <c r="P15" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q15">
-        <v>1</v>
-      </c>
-      <c r="R15" t="b">
-        <v>0</v>
-      </c>
-      <c r="S15" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>11485</v>
-      </c>
-      <c r="B16" s="12">
-        <v>46057</v>
-      </c>
-      <c r="C16" s="12">
-        <v>1.4312500000014601</v>
-      </c>
-      <c r="D16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16">
-        <v>55</v>
-      </c>
-      <c r="H16">
-        <v>1.6890000104904199</v>
-      </c>
-      <c r="I16" t="s">
-        <v>42</v>
-      </c>
-      <c r="J16" t="s">
-        <v>63</v>
-      </c>
-      <c r="K16" t="s">
-        <v>44</v>
-      </c>
-      <c r="L16" t="s">
-        <v>45</v>
-      </c>
-      <c r="M16" t="b">
-        <v>1</v>
-      </c>
-      <c r="N16" t="b">
-        <v>0</v>
-      </c>
-      <c r="O16" t="b">
-        <v>1</v>
-      </c>
-      <c r="P16" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q16">
-        <v>1</v>
-      </c>
-      <c r="R16" t="b">
-        <v>0</v>
-      </c>
-      <c r="S16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>11485</v>
-      </c>
-      <c r="B17" s="12">
-        <v>46057</v>
-      </c>
-      <c r="C17" s="12">
-        <v>1.4312500000014601</v>
-      </c>
-      <c r="D17" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" t="s">
-        <v>41</v>
-      </c>
-      <c r="G17">
-        <v>52</v>
-      </c>
-      <c r="H17">
-        <v>1.6311000585555999</v>
-      </c>
-      <c r="I17" t="s">
-        <v>42</v>
-      </c>
-      <c r="J17" t="s">
-        <v>63</v>
-      </c>
-      <c r="K17" t="s">
-        <v>44</v>
-      </c>
-      <c r="L17" t="s">
-        <v>45</v>
-      </c>
-      <c r="M17" t="b">
-        <v>1</v>
-      </c>
-      <c r="N17" t="b">
-        <v>0</v>
-      </c>
-      <c r="O17" t="b">
-        <v>1</v>
-      </c>
-      <c r="P17" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q17">
-        <v>1</v>
-      </c>
-      <c r="R17" t="b">
-        <v>0</v>
-      </c>
-      <c r="S17" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>11485</v>
-      </c>
-      <c r="B18" s="12">
-        <v>46057</v>
-      </c>
-      <c r="C18" s="12">
-        <v>1.4312500000014601</v>
-      </c>
-      <c r="D18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G18">
-        <v>56</v>
-      </c>
-      <c r="H18">
-        <v>1.9307999610900899</v>
-      </c>
-      <c r="I18" t="s">
-        <v>42</v>
-      </c>
-      <c r="J18" t="s">
-        <v>63</v>
-      </c>
-      <c r="K18" t="s">
-        <v>44</v>
-      </c>
-      <c r="L18" t="s">
-        <v>45</v>
-      </c>
-      <c r="M18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" t="b">
-        <v>1</v>
-      </c>
-      <c r="P18" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q18">
-        <v>1</v>
-      </c>
-      <c r="R18" t="b">
-        <v>0</v>
-      </c>
-      <c r="S18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>11485</v>
-      </c>
-      <c r="B19" s="12">
-        <v>46057</v>
-      </c>
-      <c r="C19" s="12">
-        <v>1.4312500000014601</v>
-      </c>
-      <c r="D19" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" t="s">
-        <v>54</v>
-      </c>
-      <c r="F19" t="s">
-        <v>41</v>
-      </c>
-      <c r="G19">
-        <v>49</v>
-      </c>
-      <c r="H19">
-        <v>1.16050004959106</v>
-      </c>
-      <c r="I19" t="s">
-        <v>42</v>
-      </c>
-      <c r="J19" t="s">
-        <v>43</v>
-      </c>
-      <c r="K19" t="s">
-        <v>44</v>
-      </c>
-      <c r="L19" t="s">
-        <v>45</v>
-      </c>
-      <c r="M19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N19" t="b">
-        <v>0</v>
-      </c>
-      <c r="O19" t="b">
-        <v>1</v>
-      </c>
-      <c r="P19" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q19">
-        <v>1</v>
-      </c>
-      <c r="R19" t="b">
-        <v>0</v>
-      </c>
-      <c r="S19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>11485</v>
-      </c>
-      <c r="B20" s="12">
-        <v>46057</v>
-      </c>
-      <c r="C20" s="12">
-        <v>1.4312500000014601</v>
-      </c>
-      <c r="D20" t="s">
-        <v>53</v>
-      </c>
       <c r="E20" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F20" t="s">
         <v>41</v>
       </c>
       <c r="G20">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="H20">
-        <v>1.72220003604889</v>
+        <v>0.64999997615814198</v>
       </c>
       <c r="I20" t="s">
         <v>42</v>
       </c>
       <c r="J20" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="K20" t="s">
         <v>44</v>
       </c>
       <c r="L20" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="M20" t="b">
         <v>1</v>
       </c>
       <c r="N20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="Q20">
         <v>1</v>
@@ -2003,54 +2017,54 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>11485</v>
+        <v>11496</v>
       </c>
       <c r="B21" s="12">
-        <v>46057</v>
+        <v>46066</v>
       </c>
       <c r="C21" s="12">
-        <v>1.4312500000014601</v>
+        <v>1.55069444444598</v>
       </c>
       <c r="D21" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F21" t="s">
         <v>41</v>
       </c>
       <c r="G21">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H21">
-        <v>0.85820001363754295</v>
+        <v>1.1000000238418599</v>
       </c>
       <c r="I21" t="s">
         <v>42</v>
       </c>
       <c r="J21" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="K21" t="s">
         <v>44</v>
       </c>
       <c r="L21" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="M21" t="b">
         <v>1</v>
       </c>
       <c r="N21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="Q21">
         <v>1</v>
@@ -2062,54 +2076,54 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>11485</v>
+        <v>11496</v>
       </c>
       <c r="B22" s="12">
-        <v>46057</v>
+        <v>46066</v>
       </c>
       <c r="C22" s="12">
-        <v>1.4312500000014601</v>
+        <v>1.55069444444598</v>
       </c>
       <c r="D22" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F22" t="s">
         <v>41</v>
       </c>
       <c r="G22">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="H22">
-        <v>6.1848998069763201</v>
+        <v>1.53999996185303</v>
       </c>
       <c r="I22" t="s">
         <v>42</v>
       </c>
       <c r="J22" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="K22" t="s">
         <v>44</v>
       </c>
       <c r="L22" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="M22" t="b">
         <v>1</v>
       </c>
       <c r="N22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="Q22">
         <v>1</v>
@@ -2121,54 +2135,54 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>11485</v>
+        <v>6</v>
       </c>
       <c r="B23" s="12">
-        <v>46057</v>
+        <v>46076</v>
       </c>
       <c r="C23" s="12">
-        <v>1.4312500000014601</v>
+        <v>1.47083333333285</v>
       </c>
       <c r="D23" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F23" t="s">
         <v>41</v>
       </c>
       <c r="G23">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="H23">
-        <v>5.4809999465942401</v>
+        <v>2.02</v>
       </c>
       <c r="I23" t="s">
         <v>42</v>
       </c>
       <c r="J23" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="K23" t="s">
         <v>44</v>
       </c>
       <c r="L23" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="M23" t="b">
         <v>1</v>
       </c>
       <c r="N23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="Q23">
         <v>1</v>
@@ -2177,21 +2191,21 @@
         <v>0</v>
       </c>
       <c r="S23" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B24" s="12">
-        <v>46063</v>
+        <v>46076</v>
       </c>
       <c r="C24" s="12">
-        <v>1.59375</v>
+        <v>1.47083333333285</v>
       </c>
       <c r="D24" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s">
         <v>40</v>
@@ -2200,10 +2214,10 @@
         <v>41</v>
       </c>
       <c r="G24">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H24">
-        <v>1.3</v>
+        <v>1.92</v>
       </c>
       <c r="I24" t="s">
         <v>42</v>
@@ -2227,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="Q24">
         <v>1</v>
@@ -2236,21 +2250,21 @@
         <v>0</v>
       </c>
       <c r="S24" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B25" s="12">
-        <v>46063</v>
+        <v>46076</v>
       </c>
       <c r="C25" s="12">
-        <v>1.59375</v>
+        <v>1.47083333333285</v>
       </c>
       <c r="D25" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
         <v>40</v>
@@ -2259,10 +2273,10 @@
         <v>41</v>
       </c>
       <c r="G25">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="H25">
-        <v>1.28</v>
+        <v>2.92</v>
       </c>
       <c r="I25" t="s">
         <v>42</v>
@@ -2286,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="Q25">
         <v>1</v>
@@ -2295,21 +2309,21 @@
         <v>0</v>
       </c>
       <c r="S25" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>3</v>
+        <v>11544</v>
       </c>
       <c r="B26" s="12">
-        <v>46063</v>
+        <v>46076</v>
       </c>
       <c r="C26" s="12">
-        <v>1.59375</v>
+        <v>1.38541666666788</v>
       </c>
       <c r="D26" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E26" t="s">
         <v>40</v>
@@ -2318,10 +2332,10 @@
         <v>41</v>
       </c>
       <c r="G26">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H26">
-        <v>1.08</v>
+        <v>1.5599999427795399</v>
       </c>
       <c r="I26" t="s">
         <v>42</v>
@@ -2345,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="Q26">
         <v>1</v>
@@ -2354,21 +2368,21 @@
         <v>0</v>
       </c>
       <c r="S26" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>4</v>
+        <v>11544</v>
       </c>
       <c r="B27" s="12">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="C27" s="12">
-        <v>1.4034722222204401</v>
+        <v>1.38541666666788</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E27" t="s">
         <v>40</v>
@@ -2377,10 +2391,10 @@
         <v>41</v>
       </c>
       <c r="G27">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H27">
-        <v>1.78</v>
+        <v>1.5599999427795399</v>
       </c>
       <c r="I27" t="s">
         <v>42</v>
@@ -2404,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="Q27">
         <v>1</v>
@@ -2416,18 +2430,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>4</v>
+        <v>11544</v>
       </c>
       <c r="B28" s="12">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="C28" s="12">
-        <v>1.4034722222204401</v>
+        <v>1.38541666666788</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E28" t="s">
         <v>40</v>
@@ -2436,10 +2450,10 @@
         <v>41</v>
       </c>
       <c r="G28">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H28">
-        <v>2.11</v>
+        <v>1.7799999713897701</v>
       </c>
       <c r="I28" t="s">
         <v>42</v>
@@ -2463,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="Q28">
         <v>1</v>
@@ -2475,18 +2489,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>4</v>
+        <v>11546</v>
       </c>
       <c r="B29" s="12">
-        <v>46064</v>
+        <v>46079</v>
       </c>
       <c r="C29" s="12">
-        <v>1.4034722222204401</v>
+        <v>1.42222222222335</v>
       </c>
       <c r="D29" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E29" t="s">
         <v>40</v>
@@ -2495,10 +2509,10 @@
         <v>41</v>
       </c>
       <c r="G29">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H29">
-        <v>1.97</v>
+        <v>1.4800000190734901</v>
       </c>
       <c r="I29" t="s">
         <v>42</v>
@@ -2522,7 +2536,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="Q29">
         <v>1</v>
@@ -2531,21 +2545,21 @@
         <v>0</v>
       </c>
       <c r="S29" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>11517</v>
+        <v>11546</v>
       </c>
       <c r="B30" s="12">
-        <v>46064</v>
+        <v>46079</v>
       </c>
       <c r="C30" s="12">
-        <v>1.34375</v>
+        <v>1.42222222222335</v>
       </c>
       <c r="D30" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="E30" t="s">
         <v>40</v>
@@ -2554,10 +2568,10 @@
         <v>41</v>
       </c>
       <c r="G30">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H30">
-        <v>1.08000004291534</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="I30" t="s">
         <v>42</v>
@@ -2581,7 +2595,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="Q30">
         <v>1</v>
@@ -2590,21 +2604,21 @@
         <v>0</v>
       </c>
       <c r="S30" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>11517</v>
+        <v>11546</v>
       </c>
       <c r="B31" s="12">
-        <v>46064</v>
+        <v>46079</v>
       </c>
       <c r="C31" s="12">
-        <v>1.34375</v>
+        <v>1.42222222222335</v>
       </c>
       <c r="D31" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="E31" t="s">
         <v>40</v>
@@ -2613,10 +2627,10 @@
         <v>41</v>
       </c>
       <c r="G31">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H31">
-        <v>0.91000002622604403</v>
+        <v>1.70000004768372</v>
       </c>
       <c r="I31" t="s">
         <v>42</v>
@@ -2640,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="Q31">
         <v>1</v>
@@ -2649,21 +2663,21 @@
         <v>0</v>
       </c>
       <c r="S31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>11517</v>
+        <v>11532</v>
       </c>
       <c r="B32" s="12">
-        <v>46064</v>
+        <v>46079</v>
       </c>
       <c r="C32" s="12">
-        <v>1.34375</v>
+        <v>1.49652777777737</v>
       </c>
       <c r="D32" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E32" t="s">
         <v>40</v>
@@ -2672,57 +2686,57 @@
         <v>41</v>
       </c>
       <c r="G32">
+        <v>54</v>
+      </c>
+      <c r="H32">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="I32" t="s">
+        <v>42</v>
+      </c>
+      <c r="J32" t="s">
+        <v>43</v>
+      </c>
+      <c r="K32" t="s">
+        <v>44</v>
+      </c>
+      <c r="L32" t="s">
+        <v>55</v>
+      </c>
+      <c r="M32" t="b">
+        <v>1</v>
+      </c>
+      <c r="N32" t="b">
+        <v>1</v>
+      </c>
+      <c r="O32" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q32">
+        <v>1</v>
+      </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
+      <c r="S32" t="s">
         <v>50</v>
       </c>
-      <c r="H32">
-        <v>1.25</v>
-      </c>
-      <c r="I32" t="s">
-        <v>42</v>
-      </c>
-      <c r="J32" t="s">
-        <v>43</v>
-      </c>
-      <c r="K32" t="s">
-        <v>44</v>
-      </c>
-      <c r="L32" t="s">
-        <v>55</v>
-      </c>
-      <c r="M32" t="b">
-        <v>1</v>
-      </c>
-      <c r="N32" t="b">
-        <v>1</v>
-      </c>
-      <c r="O32" t="b">
-        <v>0</v>
-      </c>
-      <c r="P32" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q32">
-        <v>1</v>
-      </c>
-      <c r="R32" t="b">
-        <v>0</v>
-      </c>
-      <c r="S32" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>11496</v>
+        <v>11532</v>
       </c>
       <c r="B33" s="12">
-        <v>46066</v>
+        <v>46079</v>
       </c>
       <c r="C33" s="12">
-        <v>1.55069444444598</v>
+        <v>1.49652777777737</v>
       </c>
       <c r="D33" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="E33" t="s">
         <v>40</v>
@@ -2731,10 +2745,10 @@
         <v>41</v>
       </c>
       <c r="G33">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="H33">
-        <v>0.64999997615814198</v>
+        <v>2.0699999332428001</v>
       </c>
       <c r="I33" t="s">
         <v>42</v>
@@ -2758,7 +2772,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="Q33">
         <v>1</v>
@@ -2767,21 +2781,21 @@
         <v>0</v>
       </c>
       <c r="S33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>11496</v>
+        <v>11532</v>
       </c>
       <c r="B34" s="12">
-        <v>46066</v>
+        <v>46079</v>
       </c>
       <c r="C34" s="12">
-        <v>1.55069444444598</v>
+        <v>1.49652777777737</v>
       </c>
       <c r="D34" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="E34" t="s">
         <v>40</v>
@@ -2790,10 +2804,10 @@
         <v>41</v>
       </c>
       <c r="G34">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H34">
-        <v>1.1000000238418599</v>
+        <v>1.37000000476837</v>
       </c>
       <c r="I34" t="s">
         <v>42</v>
@@ -2817,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="Q34">
         <v>1</v>
@@ -2826,21 +2840,21 @@
         <v>0</v>
       </c>
       <c r="S34" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>11496</v>
+        <v>11580</v>
       </c>
       <c r="B35" s="12">
-        <v>46066</v>
+        <v>46083</v>
       </c>
       <c r="C35" s="12">
-        <v>1.55069444444598</v>
+        <v>1.4590277777788301</v>
       </c>
       <c r="D35" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="E35" t="s">
         <v>40</v>
@@ -2849,10 +2863,10 @@
         <v>41</v>
       </c>
       <c r="G35">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H35">
-        <v>1.53999996185303</v>
+        <v>1.7525000572204601</v>
       </c>
       <c r="I35" t="s">
         <v>42</v>
@@ -2876,7 +2890,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="Q35">
         <v>1</v>
@@ -2888,18 +2902,18 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>6</v>
+        <v>11580</v>
       </c>
       <c r="B36" s="12">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="C36" s="12">
-        <v>1.47083333333285</v>
+        <v>1.4590277777788301</v>
       </c>
       <c r="D36" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="E36" t="s">
         <v>40</v>
@@ -2908,10 +2922,10 @@
         <v>41</v>
       </c>
       <c r="G36">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="H36">
-        <v>2.02</v>
+        <v>1.10280001163483</v>
       </c>
       <c r="I36" t="s">
         <v>42</v>
@@ -2935,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="Q36">
         <v>1</v>
@@ -2944,21 +2958,21 @@
         <v>0</v>
       </c>
       <c r="S36" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>6</v>
+        <v>11580</v>
       </c>
       <c r="B37" s="12">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="C37" s="12">
-        <v>1.47083333333285</v>
+        <v>1.4590277777788301</v>
       </c>
       <c r="D37" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="E37" t="s">
         <v>40</v>
@@ -2967,10 +2981,10 @@
         <v>41</v>
       </c>
       <c r="G37">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H37">
-        <v>1.92</v>
+        <v>1.43700003623962</v>
       </c>
       <c r="I37" t="s">
         <v>42</v>
@@ -2994,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="Q37">
         <v>1</v>
@@ -3003,21 +3017,21 @@
         <v>0</v>
       </c>
       <c r="S37" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>6</v>
+        <v>11586</v>
       </c>
       <c r="B38" s="12">
-        <v>46076</v>
+        <v>46092</v>
       </c>
       <c r="C38" s="12">
-        <v>1.47083333333285</v>
+        <v>1.35069444444525</v>
       </c>
       <c r="D38" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="E38" t="s">
         <v>40</v>
@@ -3026,10 +3040,10 @@
         <v>41</v>
       </c>
       <c r="G38">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H38">
-        <v>2.92</v>
+        <v>2.5699999332428001</v>
       </c>
       <c r="I38" t="s">
         <v>42</v>
@@ -3053,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="Q38">
         <v>1</v>
@@ -3062,21 +3076,21 @@
         <v>0</v>
       </c>
       <c r="S38" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>11544</v>
+        <v>11586</v>
       </c>
       <c r="B39" s="12">
-        <v>46076</v>
+        <v>46092</v>
       </c>
       <c r="C39" s="12">
-        <v>1.38541666666788</v>
+        <v>1.35069444444525</v>
       </c>
       <c r="D39" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="E39" t="s">
         <v>40</v>
@@ -3085,10 +3099,10 @@
         <v>41</v>
       </c>
       <c r="G39">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H39">
-        <v>1.5599999427795399</v>
+        <v>1.58000004291534</v>
       </c>
       <c r="I39" t="s">
         <v>42</v>
@@ -3112,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="Q39">
         <v>1</v>
@@ -3121,21 +3135,21 @@
         <v>0</v>
       </c>
       <c r="S39" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>11544</v>
+        <v>11586</v>
       </c>
       <c r="B40" s="12">
-        <v>46076</v>
+        <v>46092</v>
       </c>
       <c r="C40" s="12">
-        <v>1.38541666666788</v>
+        <v>1.35069444444525</v>
       </c>
       <c r="D40" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="E40" t="s">
         <v>40</v>
@@ -3144,10 +3158,10 @@
         <v>41</v>
       </c>
       <c r="G40">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="H40">
-        <v>1.5599999427795399</v>
+        <v>1.04999995231628</v>
       </c>
       <c r="I40" t="s">
         <v>42</v>
@@ -3171,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="Q40">
         <v>1</v>
@@ -3180,21 +3194,21 @@
         <v>0</v>
       </c>
       <c r="S40" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>11544</v>
+        <v>11586</v>
       </c>
       <c r="B41" s="12">
-        <v>46076</v>
+        <v>46092</v>
       </c>
       <c r="C41" s="12">
-        <v>1.38541666666788</v>
+        <v>1.35069444444525</v>
       </c>
       <c r="D41" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="E41" t="s">
         <v>40</v>
@@ -3203,10 +3217,10 @@
         <v>41</v>
       </c>
       <c r="G41">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H41">
-        <v>1.7799999713897701</v>
+        <v>0.980000019073486</v>
       </c>
       <c r="I41" t="s">
         <v>42</v>
@@ -3230,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="Q41">
         <v>1</v>
@@ -3239,21 +3253,21 @@
         <v>0</v>
       </c>
       <c r="S41" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>11546</v>
+        <v>11586</v>
       </c>
       <c r="B42" s="12">
-        <v>46079</v>
+        <v>46092</v>
       </c>
       <c r="C42" s="12">
-        <v>1.42222222222335</v>
+        <v>1.35069444444525</v>
       </c>
       <c r="D42" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E42" t="s">
         <v>40</v>
@@ -3262,10 +3276,10 @@
         <v>41</v>
       </c>
       <c r="G42">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H42">
-        <v>1.4800000190734901</v>
+        <v>1.28999996185303</v>
       </c>
       <c r="I42" t="s">
         <v>42</v>
@@ -3289,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="Q42">
         <v>1</v>
@@ -3301,18 +3315,18 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>11546</v>
+        <v>11586</v>
       </c>
       <c r="B43" s="12">
-        <v>46079</v>
+        <v>46092</v>
       </c>
       <c r="C43" s="12">
-        <v>1.42222222222335</v>
+        <v>1.35069444444525</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E43" t="s">
         <v>40</v>
@@ -3321,10 +3335,10 @@
         <v>41</v>
       </c>
       <c r="G43">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H43">
-        <v>1.20000004768372</v>
+        <v>1.95000004768372</v>
       </c>
       <c r="I43" t="s">
         <v>42</v>
@@ -3348,7 +3362,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="Q43">
         <v>1</v>
@@ -3360,18 +3374,18 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>11546</v>
+        <v>11586</v>
       </c>
       <c r="B44" s="12">
-        <v>46079</v>
+        <v>46092</v>
       </c>
       <c r="C44" s="12">
-        <v>1.42222222222335</v>
+        <v>1.35069444444525</v>
       </c>
       <c r="D44" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E44" t="s">
         <v>40</v>
@@ -3380,10 +3394,10 @@
         <v>41</v>
       </c>
       <c r="G44">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H44">
-        <v>1.70000004768372</v>
+        <v>2.4800000190734899</v>
       </c>
       <c r="I44" t="s">
         <v>42</v>
@@ -3407,7 +3421,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="Q44">
         <v>1</v>
@@ -3419,89 +3433,89 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>11532</v>
+        <v>11562</v>
       </c>
       <c r="B45" s="12">
-        <v>46079</v>
+        <v>46094</v>
       </c>
       <c r="C45" s="12">
-        <v>1.49652777777737</v>
+        <v>1.3499999999985399</v>
       </c>
       <c r="D45" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E45" t="s">
+        <v>54</v>
+      </c>
+      <c r="F45" t="s">
+        <v>41</v>
+      </c>
+      <c r="G45">
+        <v>55</v>
+      </c>
+      <c r="H45">
+        <v>1.7799999713897701</v>
+      </c>
+      <c r="I45" t="s">
+        <v>42</v>
+      </c>
+      <c r="J45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K45" t="s">
+        <v>44</v>
+      </c>
+      <c r="L45" t="s">
+        <v>55</v>
+      </c>
+      <c r="M45" t="b">
+        <v>1</v>
+      </c>
+      <c r="N45" t="b">
+        <v>1</v>
+      </c>
+      <c r="O45" t="b">
+        <v>0</v>
+      </c>
+      <c r="P45" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q45">
+        <v>1</v>
+      </c>
+      <c r="R45" t="b">
+        <v>0</v>
+      </c>
+      <c r="S45" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>11584</v>
+      </c>
+      <c r="B46" s="12">
+        <v>46101</v>
+      </c>
+      <c r="C46" s="12">
+        <v>1.4124999999985399</v>
+      </c>
+      <c r="D46" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" t="s">
+        <v>54</v>
+      </c>
+      <c r="F46" t="s">
+        <v>41</v>
+      </c>
+      <c r="G46">
         <v>40</v>
       </c>
-      <c r="F45" t="s">
-        <v>41</v>
-      </c>
-      <c r="G45">
-        <v>54</v>
-      </c>
-      <c r="H45">
-        <v>1.70000004768372</v>
-      </c>
-      <c r="I45" t="s">
-        <v>42</v>
-      </c>
-      <c r="J45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K45" t="s">
-        <v>44</v>
-      </c>
-      <c r="L45" t="s">
-        <v>55</v>
-      </c>
-      <c r="M45" t="b">
-        <v>1</v>
-      </c>
-      <c r="N45" t="b">
-        <v>1</v>
-      </c>
-      <c r="O45" t="b">
-        <v>0</v>
-      </c>
-      <c r="P45" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q45">
-        <v>1</v>
-      </c>
-      <c r="R45" t="b">
-        <v>0</v>
-      </c>
-      <c r="S45" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A46">
-        <v>11532</v>
-      </c>
-      <c r="B46" s="12">
-        <v>46079</v>
-      </c>
-      <c r="C46" s="12">
-        <v>1.49652777777737</v>
-      </c>
-      <c r="D46" t="s">
-        <v>57</v>
-      </c>
-      <c r="E46" t="s">
-        <v>40</v>
-      </c>
-      <c r="F46" t="s">
-        <v>41</v>
-      </c>
-      <c r="G46">
-        <v>55</v>
-      </c>
       <c r="H46">
-        <v>2.0699999332428001</v>
+        <v>0.658399999141693</v>
       </c>
       <c r="I46" t="s">
         <v>42</v>
@@ -3525,7 +3539,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="Q46">
         <v>1</v>
@@ -3534,21 +3548,21 @@
         <v>0</v>
       </c>
       <c r="S46" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>11532</v>
+        <v>11437</v>
       </c>
       <c r="B47" s="12">
-        <v>46079</v>
+        <v>46036</v>
       </c>
       <c r="C47" s="12">
-        <v>1.49652777777737</v>
+        <v>1.41875000000073</v>
       </c>
       <c r="D47" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="E47" t="s">
         <v>40</v>
@@ -3557,10 +3571,10 @@
         <v>41</v>
       </c>
       <c r="G47">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="H47">
-        <v>1.37000000476837</v>
+        <v>0.37999999523162797</v>
       </c>
       <c r="I47" t="s">
         <v>42</v>
@@ -3572,19 +3586,19 @@
         <v>44</v>
       </c>
       <c r="L47" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M47" t="b">
         <v>1</v>
       </c>
       <c r="N47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="Q47">
         <v>1</v>
@@ -3593,21 +3607,21 @@
         <v>0</v>
       </c>
       <c r="S47" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>11580</v>
+        <v>11434</v>
       </c>
       <c r="B48" s="12">
-        <v>46083</v>
+        <v>46036</v>
       </c>
       <c r="C48" s="12">
-        <v>1.4590277777788301</v>
+        <v>1.48611111110949</v>
       </c>
       <c r="D48" t="s">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="E48" t="s">
         <v>40</v>
@@ -3616,10 +3630,10 @@
         <v>41</v>
       </c>
       <c r="G48">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H48">
-        <v>1.7525000572204601</v>
+        <v>0.57999998331069902</v>
       </c>
       <c r="I48" t="s">
         <v>42</v>
@@ -3631,19 +3645,19 @@
         <v>44</v>
       </c>
       <c r="L48" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M48" t="b">
         <v>1</v>
       </c>
       <c r="N48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="Q48">
         <v>1</v>
@@ -3652,21 +3666,21 @@
         <v>0</v>
       </c>
       <c r="S48" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>11580</v>
+        <v>11455</v>
       </c>
       <c r="B49" s="12">
-        <v>46083</v>
+        <v>46037</v>
       </c>
       <c r="C49" s="12">
-        <v>1.4590277777788301</v>
+        <v>1.40972222222263</v>
       </c>
       <c r="D49" t="s">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="E49" t="s">
         <v>40</v>
@@ -3675,10 +3689,10 @@
         <v>41</v>
       </c>
       <c r="G49">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H49">
-        <v>1.10280001163483</v>
+        <v>0.62999999523162797</v>
       </c>
       <c r="I49" t="s">
         <v>42</v>
@@ -3690,19 +3704,19 @@
         <v>44</v>
       </c>
       <c r="L49" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M49" t="b">
         <v>1</v>
       </c>
       <c r="N49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="Q49">
         <v>1</v>
@@ -3711,57 +3725,57 @@
         <v>0</v>
       </c>
       <c r="S49" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>11580</v>
+        <v>11485</v>
       </c>
       <c r="B50" s="12">
-        <v>46083</v>
+        <v>46057</v>
       </c>
       <c r="C50" s="12">
-        <v>1.4590277777788301</v>
+        <v>1.4312500000014601</v>
       </c>
       <c r="D50" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="E50" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F50" t="s">
         <v>41</v>
       </c>
       <c r="G50">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H50">
-        <v>1.43700003623962</v>
+        <v>1.8380000591278101</v>
       </c>
       <c r="I50" t="s">
         <v>42</v>
       </c>
       <c r="J50" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="K50" t="s">
         <v>44</v>
       </c>
       <c r="L50" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M50" t="b">
         <v>1</v>
       </c>
       <c r="N50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="Q50">
         <v>1</v>
@@ -3773,54 +3787,54 @@
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>11586</v>
+        <v>11485</v>
       </c>
       <c r="B51" s="12">
-        <v>46092</v>
+        <v>46057</v>
       </c>
       <c r="C51" s="12">
-        <v>1.35069444444525</v>
+        <v>1.4312500000014601</v>
       </c>
       <c r="D51" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="E51" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F51" t="s">
         <v>41</v>
       </c>
       <c r="G51">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="H51">
-        <v>2.5699999332428001</v>
+        <v>5.8803000450134304</v>
       </c>
       <c r="I51" t="s">
         <v>42</v>
       </c>
       <c r="J51" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="K51" t="s">
         <v>44</v>
       </c>
       <c r="L51" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M51" t="b">
         <v>1</v>
       </c>
       <c r="N51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="Q51">
         <v>1</v>
@@ -3832,54 +3846,54 @@
         <v>47</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>11586</v>
+        <v>11485</v>
       </c>
       <c r="B52" s="12">
-        <v>46092</v>
+        <v>46057</v>
       </c>
       <c r="C52" s="12">
-        <v>1.35069444444525</v>
+        <v>1.4312500000014601</v>
       </c>
       <c r="D52" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="E52" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F52" t="s">
         <v>41</v>
       </c>
       <c r="G52">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H52">
-        <v>1.58000004291534</v>
+        <v>1.6890000104904199</v>
       </c>
       <c r="I52" t="s">
         <v>42</v>
       </c>
       <c r="J52" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="K52" t="s">
         <v>44</v>
       </c>
       <c r="L52" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M52" t="b">
         <v>1</v>
       </c>
       <c r="N52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="Q52">
         <v>1</v>
@@ -3891,54 +3905,54 @@
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>11586</v>
+        <v>11485</v>
       </c>
       <c r="B53" s="12">
-        <v>46092</v>
+        <v>46057</v>
       </c>
       <c r="C53" s="12">
-        <v>1.35069444444525</v>
+        <v>1.4312500000014601</v>
       </c>
       <c r="D53" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="E53" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F53" t="s">
         <v>41</v>
       </c>
       <c r="G53">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H53">
-        <v>1.04999995231628</v>
+        <v>1.6311000585555999</v>
       </c>
       <c r="I53" t="s">
         <v>42</v>
       </c>
       <c r="J53" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="K53" t="s">
         <v>44</v>
       </c>
       <c r="L53" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M53" t="b">
         <v>1</v>
       </c>
       <c r="N53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="Q53">
         <v>1</v>
@@ -3950,54 +3964,54 @@
         <v>47</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>11586</v>
+        <v>11485</v>
       </c>
       <c r="B54" s="12">
-        <v>46092</v>
+        <v>46057</v>
       </c>
       <c r="C54" s="12">
-        <v>1.35069444444525</v>
+        <v>1.4312500000014601</v>
       </c>
       <c r="D54" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="E54" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F54" t="s">
         <v>41</v>
       </c>
       <c r="G54">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H54">
-        <v>0.980000019073486</v>
+        <v>1.9307999610900899</v>
       </c>
       <c r="I54" t="s">
         <v>42</v>
       </c>
       <c r="J54" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="K54" t="s">
         <v>44</v>
       </c>
       <c r="L54" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M54" t="b">
         <v>1</v>
       </c>
       <c r="N54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="Q54">
         <v>1</v>
@@ -4009,30 +4023,30 @@
         <v>47</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>11586</v>
+        <v>11485</v>
       </c>
       <c r="B55" s="12">
-        <v>46092</v>
+        <v>46057</v>
       </c>
       <c r="C55" s="12">
-        <v>1.35069444444525</v>
+        <v>1.4312500000014601</v>
       </c>
       <c r="D55" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="E55" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F55" t="s">
         <v>41</v>
       </c>
       <c r="G55">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H55">
-        <v>1.28999996185303</v>
+        <v>1.16050004959106</v>
       </c>
       <c r="I55" t="s">
         <v>42</v>
@@ -4044,19 +4058,19 @@
         <v>44</v>
       </c>
       <c r="L55" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M55" t="b">
         <v>1</v>
       </c>
       <c r="N55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="Q55">
         <v>1</v>
@@ -4068,54 +4082,54 @@
         <v>47</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>11586</v>
+        <v>11485</v>
       </c>
       <c r="B56" s="12">
-        <v>46092</v>
+        <v>46057</v>
       </c>
       <c r="C56" s="12">
-        <v>1.35069444444525</v>
+        <v>1.4312500000014601</v>
       </c>
       <c r="D56" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="E56" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F56" t="s">
         <v>41</v>
       </c>
       <c r="G56">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H56">
-        <v>1.95000004768372</v>
+        <v>1.72220003604889</v>
       </c>
       <c r="I56" t="s">
         <v>42</v>
       </c>
       <c r="J56" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="K56" t="s">
         <v>44</v>
       </c>
       <c r="L56" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M56" t="b">
         <v>1</v>
       </c>
       <c r="N56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="Q56">
         <v>1</v>
@@ -4127,54 +4141,54 @@
         <v>47</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>11586</v>
+        <v>11485</v>
       </c>
       <c r="B57" s="12">
-        <v>46092</v>
+        <v>46057</v>
       </c>
       <c r="C57" s="12">
-        <v>1.35069444444525</v>
+        <v>1.4312500000014601</v>
       </c>
       <c r="D57" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="E57" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F57" t="s">
         <v>41</v>
       </c>
       <c r="G57">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="H57">
-        <v>2.4800000190734899</v>
+        <v>0.85820001363754295</v>
       </c>
       <c r="I57" t="s">
         <v>42</v>
       </c>
       <c r="J57" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="K57" t="s">
         <v>44</v>
       </c>
       <c r="L57" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M57" t="b">
         <v>1</v>
       </c>
       <c r="N57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="Q57">
         <v>1</v>
@@ -4186,15 +4200,15 @@
         <v>47</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>11562</v>
+        <v>11485</v>
       </c>
       <c r="B58" s="12">
-        <v>46094</v>
+        <v>46057</v>
       </c>
       <c r="C58" s="12">
-        <v>1.3499999999985399</v>
+        <v>1.4312500000014601</v>
       </c>
       <c r="D58" t="s">
         <v>53</v>
@@ -4206,34 +4220,34 @@
         <v>41</v>
       </c>
       <c r="G58">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="H58">
-        <v>1.7799999713897701</v>
+        <v>6.1848998069763201</v>
       </c>
       <c r="I58" t="s">
         <v>42</v>
       </c>
       <c r="J58" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="K58" t="s">
         <v>44</v>
       </c>
       <c r="L58" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M58" t="b">
         <v>1</v>
       </c>
       <c r="N58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="Q58">
         <v>1</v>
@@ -4245,15 +4259,15 @@
         <v>47</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>11584</v>
+        <v>11485</v>
       </c>
       <c r="B59" s="12">
-        <v>46101</v>
+        <v>46057</v>
       </c>
       <c r="C59" s="12">
-        <v>1.4124999999985399</v>
+        <v>1.4312500000014601</v>
       </c>
       <c r="D59" t="s">
         <v>53</v>
@@ -4265,34 +4279,34 @@
         <v>41</v>
       </c>
       <c r="G59">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="H59">
-        <v>0.658399999141693</v>
+        <v>5.4809999465942401</v>
       </c>
       <c r="I59" t="s">
         <v>42</v>
       </c>
       <c r="J59" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="K59" t="s">
         <v>44</v>
       </c>
       <c r="L59" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M59" t="b">
         <v>1</v>
       </c>
       <c r="N59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="Q59">
         <v>1</v>
@@ -4305,6 +4319,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S59">
+    <sortCondition ref="O2:O59"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -4313,9 +4330,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
@@ -4341,7 +4358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>10</v>
       </c>
@@ -4364,7 +4381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>10</v>
       </c>
@@ -4390,7 +4407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>10</v>
       </c>
@@ -4416,7 +4433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>10</v>
       </c>
@@ -4442,7 +4459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>10</v>
       </c>
@@ -4468,7 +4485,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>10</v>
       </c>
@@ -4494,7 +4511,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>10</v>
       </c>
@@ -4520,7 +4537,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
@@ -4546,7 +4563,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>10</v>
       </c>
@@ -4569,7 +4586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
@@ -4592,7 +4609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>10</v>
       </c>
@@ -4622,56 +4639,61 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58354895-953B-45E0-B569-EACAE65873F3}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1">
-        <v>58</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4">
-        <v>8</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -4681,14 +4703,57 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08984375" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -4696,7 +4761,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="13">
         <v>46036</v>
       </c>
@@ -4704,7 +4769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="13">
         <v>46037</v>
       </c>
@@ -4712,7 +4777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="13">
         <v>46044</v>
       </c>
@@ -4720,7 +4785,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
         <v>46045</v>
       </c>
@@ -4728,7 +4793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
         <v>46057</v>
       </c>
@@ -4736,7 +4801,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
         <v>46063</v>
       </c>
@@ -4744,7 +4809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
         <v>46064</v>
       </c>
@@ -4752,7 +4817,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
         <v>46066</v>
       </c>
@@ -4760,7 +4825,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
         <v>46076</v>
       </c>
@@ -4768,7 +4833,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
         <v>46079</v>
       </c>
@@ -4776,7 +4841,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
         <v>46083</v>
       </c>
@@ -4784,7 +4849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
         <v>46092</v>
       </c>
@@ -4792,7 +4857,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
         <v>46094</v>
       </c>
@@ -4800,7 +4865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <v>46101</v>
       </c>
